--- a/Gerard i Òscar/PP_GerardMoreno_ÒscarLosada_M1.xlsx
+++ b/Gerard i Òscar/PP_GerardMoreno_ÒscarLosada_M1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uab-my.sharepoint.com/personal/1598367_uab_cat/Documents/5è CURS/LACE/Lab LACE - Gerard i Òscar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deumenec/Documents/Uni/LACE/Gerard i Òscar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1178" documentId="11_E8931E16AFA74F89802417BE289C22AF85259CF7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB6696ED-D794-41CB-B495-34DFCB26F806}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90AEE8C-6547-D547-8757-3D9E0C2BA823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pràctica P" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1081,7 +1081,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1244,158 +1244,152 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1417,7 +1411,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1858,7 +1852,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2296,7 +2290,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2519,6 +2513,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-67FA-384A-BE32-28D9A1A631C5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:trendline>
             <c:spPr>
@@ -2669,7 +2668,7 @@
             <c:numRef>
               <c:f>'Pràctica P'!$G$19:$G$22</c:f>
               <c:numCache>
-                <c:formatCode>0,000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -2927,7 +2926,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3313,7 +3312,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="es-ES"/>
+              <a:endParaRPr lang="es-ES_tradnl"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3517,7 +3516,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6693,12 +6692,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -7046,14 +7041,14 @@
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="89" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
     </row>
     <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7062,14 +7057,14 @@
       </c>
     </row>
     <row r="9" spans="1:17" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7428,18 +7423,18 @@
       <c r="M24" s="13"/>
     </row>
     <row r="25" spans="1:19" ht="300" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="59"/>
-      <c r="B25" s="60"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="61"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="60"/>
-      <c r="J25" s="60"/>
-      <c r="K25" s="60"/>
-      <c r="L25" s="60"/>
-      <c r="M25" s="61"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="95"/>
+      <c r="C25" s="95"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="96"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="96"/>
     </row>
     <row r="26" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7460,14 +7455,14 @@
       <c r="S27" s="9"/>
     </row>
     <row r="28" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="63" t="s">
+      <c r="A28" s="89" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
       <c r="H28" s="3" t="s">
         <v>19</v>
       </c>
@@ -7618,14 +7613,13 @@
       <c r="J32" s="6">
         <v>3.2527676938492656</v>
       </c>
-      <c r="K32" s="106">
+      <c r="K32" s="6">
         <v>0.12189535544389778</v>
       </c>
-      <c r="L32" s="106"/>
       <c r="O32" s="6">
         <v>1.9911862269162199</v>
       </c>
-      <c r="P32" s="106">
+      <c r="P32" s="6">
         <v>5.1852897256505832E-6</v>
       </c>
     </row>
@@ -7641,36 +7635,36 @@
       <c r="H33" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="K33" s="108" t="s">
+      <c r="K33" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="L33" s="105"/>
+      <c r="L33" s="53"/>
       <c r="M33" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="P33" s="105"/>
+      <c r="P33" s="53"/>
     </row>
     <row r="34" spans="1:16" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="64" t="s">
+      <c r="A34" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="65"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="66"/>
+      <c r="B34" s="91"/>
+      <c r="C34" s="91"/>
+      <c r="D34" s="91"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92"/>
     </row>
     <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H36" s="67" t="s">
+      <c r="H36" s="104" t="s">
         <v>108</v>
       </c>
-      <c r="I36" s="67"/>
-      <c r="J36" s="67"/>
-      <c r="K36" s="67"/>
+      <c r="I36" s="104"/>
+      <c r="J36" s="104"/>
+      <c r="K36" s="104"/>
     </row>
     <row r="37" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
@@ -7914,53 +7908,53 @@
       <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:16" ht="300" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="59"/>
-      <c r="B47" s="60"/>
-      <c r="C47" s="60"/>
-      <c r="D47" s="60"/>
-      <c r="E47" s="60"/>
-      <c r="F47" s="61"/>
-      <c r="H47" s="62"/>
-      <c r="I47" s="62"/>
-      <c r="J47" s="62"/>
-      <c r="K47" s="62"/>
-      <c r="L47" s="62"/>
-      <c r="M47" s="62"/>
+      <c r="A47" s="94"/>
+      <c r="B47" s="95"/>
+      <c r="C47" s="95"/>
+      <c r="D47" s="95"/>
+      <c r="E47" s="95"/>
+      <c r="F47" s="96"/>
+      <c r="H47" s="93"/>
+      <c r="I47" s="93"/>
+      <c r="J47" s="93"/>
+      <c r="K47" s="93"/>
+      <c r="L47" s="93"/>
+      <c r="M47" s="93"/>
     </row>
     <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B48" s="58" t="s">
+      <c r="B48" s="97" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="58"/>
+      <c r="C48" s="97"/>
       <c r="D48" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E48" s="69">
+      <c r="E48" s="102">
         <f>J39/I37*SQRT(1+1/E49+(C55-I43)^2/(I37^2*I44))</f>
         <v>1.2508998764146843E-2</v>
       </c>
-      <c r="F48" s="69"/>
+      <c r="F48" s="102"/>
       <c r="G48" s="14"/>
     </row>
     <row r="49" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B49" s="58" t="s">
+      <c r="B49" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="C49" s="58"/>
+      <c r="C49" s="97"/>
       <c r="D49" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E49" s="58">
+      <c r="E49" s="97">
         <f>COUNT(A38:A44)</f>
         <v>5</v>
       </c>
-      <c r="F49" s="58"/>
+      <c r="F49" s="97"/>
       <c r="G49" s="14"/>
     </row>
     <row r="50" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7990,14 +7984,14 @@
       <c r="S51" s="9"/>
     </row>
     <row r="52" spans="1:19" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="63" t="s">
+      <c r="A52" s="89" t="s">
         <v>109</v>
       </c>
-      <c r="B52" s="63"/>
-      <c r="C52" s="63"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
-      <c r="F52" s="63"/>
+      <c r="B52" s="89"/>
+      <c r="C52" s="89"/>
+      <c r="D52" s="89"/>
+      <c r="E52" s="89"/>
+      <c r="F52" s="89"/>
       <c r="H52" s="9"/>
       <c r="I52" s="9"/>
       <c r="J52" s="9"/>
@@ -8047,11 +8041,11 @@
       <c r="C55" s="3">
         <v>166.40700000000001</v>
       </c>
-      <c r="D55" s="107">
+      <c r="D55" s="87">
         <f>(C55-J37)/I37*B55</f>
         <v>37.766445245308311</v>
       </c>
-      <c r="E55" s="107">
+      <c r="E55" s="87">
         <f>E48*I45*B55</f>
         <v>3.9809216899757605</v>
       </c>
@@ -8080,20 +8074,20 @@
       <c r="G57" s="14"/>
     </row>
     <row r="58" spans="1:19" ht="200" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="70" t="s">
+      <c r="A58" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="B58" s="71"/>
-      <c r="C58" s="71"/>
-      <c r="D58" s="71"/>
-      <c r="E58" s="71"/>
-      <c r="F58" s="72"/>
-      <c r="H58" s="62"/>
-      <c r="I58" s="62"/>
-      <c r="J58" s="62"/>
-      <c r="K58" s="62"/>
-      <c r="L58" s="62"/>
-      <c r="M58" s="62"/>
+      <c r="B58" s="100"/>
+      <c r="C58" s="100"/>
+      <c r="D58" s="100"/>
+      <c r="E58" s="100"/>
+      <c r="F58" s="101"/>
+      <c r="H58" s="93"/>
+      <c r="I58" s="93"/>
+      <c r="J58" s="93"/>
+      <c r="K58" s="93"/>
+      <c r="L58" s="93"/>
+      <c r="M58" s="93"/>
     </row>
     <row r="59" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F59" s="14"/>
@@ -8129,10 +8123,10 @@
       <c r="B62" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H62" s="68"/>
-      <c r="I62" s="68"/>
-      <c r="J62" s="68"/>
-      <c r="K62" s="68"/>
+      <c r="H62" s="106"/>
+      <c r="I62" s="106"/>
+      <c r="J62" s="106"/>
+      <c r="K62" s="106"/>
     </row>
     <row r="63" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
@@ -8185,10 +8179,10 @@
         <v>-0.59399999999999997</v>
       </c>
       <c r="C65" s="47"/>
-      <c r="D65" s="74" t="s">
+      <c r="D65" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="E65" s="75">
+      <c r="E65" s="60">
         <f>(E63-J37)/I37</f>
         <v>-4.4807791514959961E-3</v>
       </c>
@@ -8332,7 +8326,7 @@
         <f>J37</f>
         <v>1.3954702310676055</v>
       </c>
-      <c r="C75" s="73" t="s">
+      <c r="C75" s="58" t="s">
         <v>90</v>
       </c>
       <c r="E75" s="14"/>
@@ -8347,7 +8341,7 @@
         <f>J39</f>
         <v>4.9832238856246169</v>
       </c>
-      <c r="C76" s="73" t="s">
+      <c r="C76" s="58" t="s">
         <v>91</v>
       </c>
       <c r="E76" s="14"/>
@@ -8362,20 +8356,20 @@
         <f>B75+3*B76</f>
         <v>16.345141887941455</v>
       </c>
-      <c r="C77" s="73"/>
+      <c r="C77" s="58"/>
       <c r="E77" s="14"/>
       <c r="F77" s="14"/>
       <c r="G77" s="14"/>
     </row>
     <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="74" t="s">
+      <c r="A78" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="B78" s="76">
+      <c r="B78" s="61">
         <f>(B77-J37)/I37</f>
         <v>3.4215545838237743E-2</v>
       </c>
-      <c r="C78" s="77" t="s">
+      <c r="C78" s="62" t="s">
         <v>81</v>
       </c>
       <c r="D78" s="14"/>
@@ -8404,20 +8398,20 @@
       <c r="G80" s="14"/>
     </row>
     <row r="81" spans="1:24" ht="213.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="64" t="s">
+      <c r="A81" s="90" t="s">
         <v>111</v>
       </c>
-      <c r="B81" s="65"/>
-      <c r="C81" s="65"/>
-      <c r="D81" s="65"/>
-      <c r="E81" s="65"/>
-      <c r="F81" s="66"/>
-      <c r="H81" s="62"/>
-      <c r="I81" s="62"/>
-      <c r="J81" s="62"/>
-      <c r="K81" s="62"/>
-      <c r="L81" s="62"/>
-      <c r="M81" s="62"/>
+      <c r="B81" s="91"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="91"/>
+      <c r="E81" s="91"/>
+      <c r="F81" s="92"/>
+      <c r="H81" s="93"/>
+      <c r="I81" s="93"/>
+      <c r="J81" s="93"/>
+      <c r="K81" s="93"/>
+      <c r="L81" s="93"/>
+      <c r="M81" s="93"/>
     </row>
     <row r="82" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="14"/>
@@ -8491,52 +8485,52 @@
       <c r="R84" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="S84" s="78" t="s">
+      <c r="S84" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="U84" s="67" t="s">
+      <c r="U84" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="V84" s="67"/>
-      <c r="W84" s="67"/>
-      <c r="X84" s="67"/>
+      <c r="V84" s="104"/>
+      <c r="W84" s="104"/>
+      <c r="X84" s="104"/>
     </row>
     <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="80">
+      <c r="A85" s="65">
         <v>1</v>
       </c>
-      <c r="B85" s="80">
+      <c r="B85" s="65">
         <f>$J$83*C85/D85</f>
         <v>117.52</v>
       </c>
-      <c r="C85" s="81">
+      <c r="C85" s="66">
         <v>2</v>
       </c>
-      <c r="D85" s="81">
+      <c r="D85" s="66">
         <v>50</v>
       </c>
-      <c r="E85" s="82">
+      <c r="E85" s="67">
         <f>$L$83*C85/D85</f>
         <v>0.97959999999999992</v>
       </c>
-      <c r="F85" s="80">
+      <c r="F85" s="65">
         <v>380.14699999999999</v>
       </c>
-      <c r="G85" s="83">
+      <c r="G85" s="68">
         <f>$J$84/F85 -1</f>
         <v>0.14366547677608943</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Q85" s="82">
+      <c r="Q85" s="67">
         <v>0.97959999999999992</v>
       </c>
-      <c r="R85" s="97">
+      <c r="R85" s="82">
         <f>AVERAGE(F85,F94)</f>
         <v>401.459</v>
       </c>
-      <c r="S85" s="97">
+      <c r="S85" s="82">
         <f>AVERAGE(G85,G94)</f>
         <v>8.6012992000520483E-2</v>
       </c>
@@ -8545,51 +8539,51 @@
       </c>
       <c r="V85" s="37" cm="1">
         <f t="array" ref="V85:W89">LINEST(S85:S88,Q85:Q88,TRUE,TRUE)</f>
-        <v>0.15016003766433181</v>
+        <v>0.15016003766433186</v>
       </c>
       <c r="W85" s="37">
-        <v>-4.1869611111622629E-2</v>
+        <v>-4.1869611111622795E-2</v>
       </c>
       <c r="X85" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="84">
+      <c r="A86" s="69">
         <v>1</v>
       </c>
-      <c r="B86" s="84">
+      <c r="B86" s="69">
         <f>$J$83*C86/D86</f>
         <v>235.04</v>
       </c>
-      <c r="C86" s="85">
+      <c r="C86" s="70">
         <v>4</v>
       </c>
-      <c r="D86" s="85">
+      <c r="D86" s="70">
         <v>50</v>
       </c>
-      <c r="E86" s="86">
+      <c r="E86" s="71">
         <f>$L$83*C86/D86</f>
         <v>1.9591999999999998</v>
       </c>
-      <c r="F86" s="84">
+      <c r="F86" s="69">
         <v>319.11900000000003</v>
       </c>
-      <c r="G86" s="87">
+      <c r="G86" s="72">
         <f t="shared" ref="G86:G94" si="6">$J$84/F86 -1</f>
         <v>0.36237892447644926</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="Q86" s="86">
+      <c r="Q86" s="71">
         <v>1.9591999999999998</v>
       </c>
-      <c r="R86" s="98">
+      <c r="R86" s="83">
         <f>AVERAGE(F86,F93)</f>
         <v>343.08150000000001</v>
       </c>
-      <c r="S86" s="98">
+      <c r="S86" s="83">
         <f>AVERAGE(G86,G93)</f>
         <v>0.27343589590830242</v>
       </c>
@@ -8597,10 +8591,10 @@
         <v>63</v>
       </c>
       <c r="V86" s="37">
-        <v>1.1871841661251496E-2</v>
+        <v>1.187184166125148E-2</v>
       </c>
       <c r="W86" s="37">
-        <v>3.1849124886331542E-2</v>
+        <v>3.1849124886331508E-2</v>
       </c>
       <c r="X86" s="6" t="s">
         <v>68</v>
@@ -8611,7 +8605,7 @@
         <v>1</v>
       </c>
       <c r="B87" s="23">
-        <f>$J$83*C87/D87</f>
+        <f t="shared" ref="B85:B94" si="7">$J$83*C87/D87</f>
         <v>352.56</v>
       </c>
       <c r="C87" s="26">
@@ -8627,7 +8621,7 @@
       <c r="F87" s="23">
         <v>302.91500000000002</v>
       </c>
-      <c r="G87" s="88">
+      <c r="G87" s="73">
         <f t="shared" si="6"/>
         <v>0.43525741544657737</v>
       </c>
@@ -8637,11 +8631,11 @@
       <c r="Q87" s="25">
         <v>2.9388000000000001</v>
       </c>
-      <c r="R87" s="99">
+      <c r="R87" s="84">
         <f>AVERAGE(F87,F92)</f>
         <v>307.35050000000001</v>
       </c>
-      <c r="S87" s="99">
+      <c r="S87" s="84">
         <f>AVERAGE(G87,G92)</f>
         <v>0.41483929447189194</v>
       </c>
@@ -8649,48 +8643,48 @@
         <v>64</v>
       </c>
       <c r="V87" s="33">
-        <v>0.98765298907856347</v>
+        <v>0.98765298907856358</v>
       </c>
       <c r="W87" s="33">
-        <v>2.6004701575229855E-2</v>
+        <v>2.600470157522982E-2</v>
       </c>
       <c r="X87" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="89">
+      <c r="A88" s="74">
         <v>1</v>
       </c>
-      <c r="B88" s="89">
-        <f>$J$83*C88/D88</f>
+      <c r="B88" s="74">
+        <f t="shared" si="7"/>
         <v>470.08</v>
       </c>
-      <c r="C88" s="90">
+      <c r="C88" s="75">
         <v>8</v>
       </c>
-      <c r="D88" s="90">
+      <c r="D88" s="75">
         <v>50</v>
       </c>
-      <c r="E88" s="91">
+      <c r="E88" s="76">
         <f>$L$83*C88/D88</f>
         <v>3.9183999999999997</v>
       </c>
-      <c r="F88" s="89">
+      <c r="F88" s="74">
         <v>284.21100000000001</v>
       </c>
-      <c r="G88" s="92">
+      <c r="G88" s="77">
         <f t="shared" si="6"/>
         <v>0.52971208010949611</v>
       </c>
-      <c r="Q88" s="91">
+      <c r="Q88" s="76">
         <v>3.9183999999999997</v>
       </c>
-      <c r="R88" s="100">
+      <c r="R88" s="85">
         <f>AVERAGE(F88,F91)</f>
         <v>284.30600000000004</v>
       </c>
-      <c r="S88" s="100">
+      <c r="S88" s="85">
         <f>AVERAGE(G88,G91)</f>
         <v>0.52920110213258886</v>
       </c>
@@ -8698,7 +8692,7 @@
         <v>65</v>
       </c>
       <c r="V88" s="33">
-        <v>159.98252457424061</v>
+        <v>159.98252457424104</v>
       </c>
       <c r="W88" s="33">
         <v>2</v>
@@ -8708,41 +8702,41 @@
       </c>
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="93">
+      <c r="A89" s="78">
         <v>1</v>
       </c>
-      <c r="B89" s="93">
-        <f>$J$83*C89/D89</f>
+      <c r="B89" s="78">
+        <f t="shared" si="7"/>
         <v>587.6</v>
       </c>
-      <c r="C89" s="94">
+      <c r="C89" s="79">
         <v>10</v>
       </c>
-      <c r="D89" s="94">
+      <c r="D89" s="79">
         <v>50</v>
       </c>
-      <c r="E89" s="95">
+      <c r="E89" s="80">
         <f>$L$83*C89/D89</f>
         <v>4.8979999999999997</v>
       </c>
-      <c r="F89" s="93">
+      <c r="F89" s="78">
         <v>283.34300000000002</v>
       </c>
-      <c r="G89" s="96">
+      <c r="G89" s="81">
         <f t="shared" si="6"/>
         <v>0.53439823817775634</v>
       </c>
       <c r="I89" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="Q89" s="95">
+      <c r="Q89" s="80">
         <v>4.8979999999999997</v>
       </c>
-      <c r="R89" s="101">
+      <c r="R89" s="86">
         <f>AVERAGE(F89,F90)</f>
         <v>284.755</v>
       </c>
-      <c r="S89" s="101">
+      <c r="S89" s="86">
         <f>AVERAGE(G89,G90)</f>
         <v>0.52682723833393452</v>
       </c>
@@ -8750,68 +8744,68 @@
         <v>66</v>
       </c>
       <c r="V89" s="33">
-        <v>0.10818730298205678</v>
+        <v>0.1081873029820568</v>
       </c>
       <c r="W89" s="33">
-        <v>1.3524890080335241E-3</v>
+        <v>1.3524890080335206E-3</v>
       </c>
       <c r="X89" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="93">
+      <c r="A90" s="78">
         <v>1</v>
       </c>
-      <c r="B90" s="93">
-        <f>$J$83*C90/D90</f>
+      <c r="B90" s="78">
+        <f t="shared" si="7"/>
         <v>587.6</v>
       </c>
-      <c r="C90" s="94">
+      <c r="C90" s="79">
         <v>10</v>
       </c>
-      <c r="D90" s="94">
+      <c r="D90" s="79">
         <v>50</v>
       </c>
-      <c r="E90" s="95">
+      <c r="E90" s="80">
         <f>$L$83*C90/D90</f>
         <v>4.8979999999999997</v>
       </c>
-      <c r="F90" s="93">
+      <c r="F90" s="78">
         <v>286.16699999999997</v>
       </c>
-      <c r="G90" s="96">
+      <c r="G90" s="81">
         <f t="shared" si="6"/>
         <v>0.51925623849011271</v>
       </c>
       <c r="I90" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="R90" s="79"/>
-      <c r="S90" s="79"/>
+      <c r="R90" s="64"/>
+      <c r="S90" s="64"/>
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="89">
+      <c r="A91" s="74">
         <v>1</v>
       </c>
-      <c r="B91" s="89">
-        <f>$J$83*C91/D91</f>
+      <c r="B91" s="74">
+        <f t="shared" si="7"/>
         <v>470.08</v>
       </c>
-      <c r="C91" s="90">
+      <c r="C91" s="75">
         <v>8</v>
       </c>
-      <c r="D91" s="90">
+      <c r="D91" s="75">
         <v>50</v>
       </c>
-      <c r="E91" s="91">
+      <c r="E91" s="76">
         <f>$L$83*C91/D91</f>
         <v>3.9183999999999997</v>
       </c>
-      <c r="F91" s="89">
+      <c r="F91" s="74">
         <v>284.40100000000001</v>
       </c>
-      <c r="G91" s="92">
+      <c r="G91" s="77">
         <f t="shared" si="6"/>
         <v>0.52869012415568162</v>
       </c>
@@ -8828,7 +8822,7 @@
         <v>1</v>
       </c>
       <c r="B92" s="23">
-        <f>$J$83*C92/D92</f>
+        <f t="shared" si="7"/>
         <v>352.56</v>
       </c>
       <c r="C92" s="26">
@@ -8844,7 +8838,7 @@
       <c r="F92" s="23">
         <v>311.786</v>
       </c>
-      <c r="G92" s="88">
+      <c r="G92" s="73">
         <f t="shared" si="6"/>
         <v>0.39442117349720651</v>
       </c>
@@ -8860,27 +8854,27 @@
       </c>
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="84">
+      <c r="A93" s="69">
         <v>1</v>
       </c>
-      <c r="B93" s="84">
-        <f>$J$83*C93/D93</f>
+      <c r="B93" s="69">
+        <f t="shared" si="7"/>
         <v>235.04</v>
       </c>
-      <c r="C93" s="85">
+      <c r="C93" s="70">
         <v>4</v>
       </c>
-      <c r="D93" s="85">
+      <c r="D93" s="70">
         <v>50</v>
       </c>
-      <c r="E93" s="86">
+      <c r="E93" s="71">
         <f>$L$83*C93/D93</f>
         <v>1.9591999999999998</v>
       </c>
-      <c r="F93" s="84">
+      <c r="F93" s="69">
         <v>367.04399999999998</v>
       </c>
-      <c r="G93" s="87">
+      <c r="G93" s="72">
         <f t="shared" si="6"/>
         <v>0.18449286734015558</v>
       </c>
@@ -8896,27 +8890,27 @@
       </c>
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="80">
+      <c r="A94" s="65">
         <v>1</v>
       </c>
-      <c r="B94" s="80">
+      <c r="B94" s="65">
         <f>$J$83*C94/D94</f>
         <v>117.52</v>
       </c>
-      <c r="C94" s="81">
+      <c r="C94" s="66">
         <v>2</v>
       </c>
-      <c r="D94" s="81">
+      <c r="D94" s="66">
         <v>50</v>
       </c>
-      <c r="E94" s="82">
+      <c r="E94" s="67">
         <f>$L$83*C94/D94</f>
         <v>0.97959999999999992</v>
       </c>
-      <c r="F94" s="80">
+      <c r="F94" s="65">
         <v>422.77100000000002</v>
       </c>
-      <c r="G94" s="83">
+      <c r="G94" s="68">
         <f t="shared" si="6"/>
         <v>2.8360507224951537E-2</v>
       </c>
@@ -8950,23 +8944,23 @@
       <c r="M96" s="13"/>
     </row>
     <row r="97" spans="1:17" ht="300" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="59"/>
-      <c r="B97" s="60"/>
-      <c r="C97" s="60"/>
-      <c r="D97" s="60"/>
-      <c r="E97" s="60"/>
-      <c r="F97" s="61"/>
-      <c r="H97" s="59"/>
-      <c r="I97" s="60"/>
-      <c r="J97" s="60"/>
-      <c r="K97" s="60"/>
-      <c r="L97" s="60"/>
-      <c r="M97" s="61"/>
-      <c r="O97" s="102" t="s">
+      <c r="A97" s="94"/>
+      <c r="B97" s="95"/>
+      <c r="C97" s="95"/>
+      <c r="D97" s="95"/>
+      <c r="E97" s="95"/>
+      <c r="F97" s="96"/>
+      <c r="H97" s="94"/>
+      <c r="I97" s="95"/>
+      <c r="J97" s="95"/>
+      <c r="K97" s="95"/>
+      <c r="L97" s="95"/>
+      <c r="M97" s="96"/>
+      <c r="O97" s="103" t="s">
         <v>110</v>
       </c>
-      <c r="P97" s="102"/>
-      <c r="Q97" s="102"/>
+      <c r="P97" s="103"/>
+      <c r="Q97" s="103"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="9"/>
@@ -8979,22 +8973,22 @@
       <c r="H98" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I98" s="58" t="s">
+      <c r="I98" s="97" t="s">
         <v>112</v>
       </c>
-      <c r="J98" s="58"/>
-      <c r="K98" s="74" t="s">
+      <c r="J98" s="97"/>
+      <c r="K98" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="L98" s="104" t="s">
+      <c r="L98" s="98" t="s">
         <v>114</v>
       </c>
-      <c r="M98" s="104"/>
-      <c r="O98" s="103" t="s">
+      <c r="M98" s="98"/>
+      <c r="O98" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="P98" s="103"/>
-      <c r="Q98" s="103"/>
+      <c r="P98" s="105"/>
+      <c r="Q98" s="105"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="9"/>
@@ -9007,20 +9001,20 @@
       <c r="H99" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I99" s="58" t="s">
+      <c r="I99" s="97" t="s">
         <v>113</v>
       </c>
-      <c r="J99" s="58"/>
+      <c r="J99" s="97"/>
       <c r="K99" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L99" s="58">
+      <c r="L99" s="97">
         <v>4</v>
       </c>
-      <c r="M99" s="58"/>
-      <c r="O99" s="103"/>
-      <c r="P99" s="103"/>
-      <c r="Q99" s="103"/>
+      <c r="M99" s="97"/>
+      <c r="O99" s="105"/>
+      <c r="P99" s="105"/>
+      <c r="Q99" s="105"/>
     </row>
     <row r="100" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="9"/>
@@ -9030,9 +9024,9 @@
       <c r="E100" s="14"/>
       <c r="F100" s="14"/>
       <c r="G100" s="14"/>
-      <c r="O100" s="103"/>
-      <c r="P100" s="103"/>
-      <c r="Q100" s="103"/>
+      <c r="O100" s="105"/>
+      <c r="P100" s="105"/>
+      <c r="Q100" s="105"/>
     </row>
     <row r="101" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
@@ -9044,19 +9038,19 @@
       <c r="E101" s="14"/>
       <c r="F101" s="14"/>
       <c r="G101" s="14"/>
-      <c r="O101" s="103"/>
-      <c r="P101" s="103"/>
-      <c r="Q101" s="103"/>
+      <c r="O101" s="105"/>
+      <c r="P101" s="105"/>
+      <c r="Q101" s="105"/>
     </row>
     <row r="102" spans="1:17" ht="300" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="63" t="s">
+      <c r="A102" s="89" t="s">
         <v>104</v>
       </c>
-      <c r="B102" s="63"/>
-      <c r="C102" s="63"/>
-      <c r="D102" s="63"/>
-      <c r="E102" s="63"/>
-      <c r="F102" s="63"/>
+      <c r="B102" s="89"/>
+      <c r="C102" s="89"/>
+      <c r="D102" s="89"/>
+      <c r="E102" s="89"/>
+      <c r="F102" s="89"/>
     </row>
     <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="14"/>
@@ -9102,11 +9096,8 @@
     <mergeCell ref="H25:M25"/>
     <mergeCell ref="H36:K36"/>
     <mergeCell ref="H62:K62"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="L99:M99"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="H58:M58"/>
     <mergeCell ref="B48:C48"/>
@@ -9116,8 +9107,11 @@
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A47:F47"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="L99:M99"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="H81:M81"/>
